--- a/Experiment3/Workspace/Models/data/35/eHMI_T_results.xlsx
+++ b/Experiment3/Workspace/Models/data/35/eHMI_T_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,81 +772,81 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>C15</t>
+          <t>C16</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" t="n">
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>C16</t>
+          <t>C17</t>
         </is>
       </c>
     </row>
@@ -855,19 +855,19 @@
         <v>5</v>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>4</v>
@@ -876,17 +876,17 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>C18</t>
         </is>
       </c>
     </row>
@@ -895,38 +895,38 @@
         <v>5</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>5</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>C18</t>
+          <t>C19</t>
         </is>
       </c>
     </row>
@@ -935,198 +935,198 @@
         <v>5</v>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>C19</t>
+          <t>C2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B14" t="n">
         <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C20</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>C20</t>
+          <t>C21</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>C21</t>
+          <t>C22</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B17" t="n">
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>C22</t>
+          <t>C23</t>
         </is>
       </c>
     </row>
@@ -1135,38 +1135,38 @@
         <v>6</v>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
         <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>C23</t>
+          <t>C24</t>
         </is>
       </c>
     </row>
@@ -1175,22 +1175,22 @@
         <v>6</v>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
@@ -1199,54 +1199,54 @@
         <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>C24</t>
+          <t>C26</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
         <v>5</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>C25</t>
+          <t>C27</t>
         </is>
       </c>
     </row>
@@ -1255,38 +1255,38 @@
         <v>6</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>C26</t>
+          <t>C28</t>
         </is>
       </c>
     </row>
@@ -1298,35 +1298,35 @@
         <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>C27</t>
+          <t>C29</t>
         </is>
       </c>
     </row>
@@ -1335,25 +1335,25 @@
         <v>6</v>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
         <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
@@ -1362,11 +1362,11 @@
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>C28</t>
+          <t>C32</t>
         </is>
       </c>
     </row>
@@ -1375,38 +1375,26 @@
         <v>6</v>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
         <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
         <v>6</v>
       </c>
-      <c r="F24" t="n">
-        <v>5</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" t="n">
-        <v>4</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>6</v>
-      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>C29</t>
+          <t>C32</t>
         </is>
       </c>
     </row>
@@ -1415,38 +1403,38 @@
         <v>6</v>
       </c>
       <c r="B25" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F25" t="n">
         <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C33</t>
         </is>
       </c>
     </row>
@@ -1455,38 +1443,26 @@
         <v>6</v>
       </c>
       <c r="B26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
         <v>6</v>
       </c>
-      <c r="F26" t="n">
-        <v>5</v>
-      </c>
-      <c r="G26" t="n">
-        <v>3</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>5</v>
-      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>C30</t>
+          <t>C33</t>
         </is>
       </c>
     </row>
@@ -1507,13 +1483,13 @@
         <v>6</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
         <v>2</v>
@@ -1522,11 +1498,11 @@
         <v>4</v>
       </c>
       <c r="K27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>C31</t>
+          <t>C34</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1530,7 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>C31</t>
+          <t>C34</t>
         </is>
       </c>
     </row>
@@ -1563,13 +1539,13 @@
         <v>6</v>
       </c>
       <c r="B29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
         <v>6</v>
@@ -1581,20 +1557,20 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>C32</t>
+          <t>C4</t>
         </is>
       </c>
     </row>
@@ -1603,26 +1579,38 @@
         <v>6</v>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>6</v>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>5</v>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>C32</t>
+          <t>C5</t>
         </is>
       </c>
     </row>
@@ -1631,75 +1619,87 @@
         <v>6</v>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>C33</t>
+          <t>C6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E32" t="n">
-        <v>6</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>8</v>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>C33</t>
+          <t>C7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C33" t="n">
         <v>6</v>
@@ -1708,29 +1708,29 @@
         <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C8</t>
         </is>
       </c>
     </row>
@@ -1750,253 +1750,25 @@
       <c r="E34" t="n">
         <v>6</v>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>7</v>
+      </c>
       <c r="L34" t="inlineStr">
-        <is>
-          <t>C34</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>6</v>
-      </c>
-      <c r="B35" t="n">
-        <v>6</v>
-      </c>
-      <c r="C35" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" t="n">
-        <v>6</v>
-      </c>
-      <c r="E35" t="n">
-        <v>6</v>
-      </c>
-      <c r="F35" t="n">
-        <v>5</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" t="n">
-        <v>5</v>
-      </c>
-      <c r="J35" t="n">
-        <v>5</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>6</v>
-      </c>
-      <c r="B36" t="n">
-        <v>5</v>
-      </c>
-      <c r="C36" t="n">
-        <v>10</v>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="n">
-        <v>2</v>
-      </c>
-      <c r="F36" t="n">
-        <v>4</v>
-      </c>
-      <c r="G36" t="n">
-        <v>3</v>
-      </c>
-      <c r="H36" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" t="n">
-        <v>5</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>5</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>C5</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>6</v>
-      </c>
-      <c r="B37" t="n">
-        <v>10</v>
-      </c>
-      <c r="C37" t="n">
-        <v>8</v>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="n">
-        <v>2</v>
-      </c>
-      <c r="F37" t="n">
-        <v>5</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" t="n">
-        <v>3</v>
-      </c>
-      <c r="J37" t="n">
-        <v>4</v>
-      </c>
-      <c r="K37" t="n">
-        <v>7</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>7</v>
-      </c>
-      <c r="B38" t="n">
-        <v>9</v>
-      </c>
-      <c r="C38" t="n">
-        <v>9</v>
-      </c>
-      <c r="D38" t="n">
-        <v>9</v>
-      </c>
-      <c r="E38" t="n">
-        <v>4</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="n">
-        <v>5</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>8</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>C7</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>5</v>
-      </c>
-      <c r="B39" t="n">
-        <v>7</v>
-      </c>
-      <c r="C39" t="n">
-        <v>6</v>
-      </c>
-      <c r="D39" t="n">
-        <v>6</v>
-      </c>
-      <c r="E39" t="n">
-        <v>5</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="n">
-        <v>4</v>
-      </c>
-      <c r="H39" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>7</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>C8</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>6</v>
-      </c>
-      <c r="B40" t="n">
-        <v>6</v>
-      </c>
-      <c r="C40" t="n">
-        <v>6</v>
-      </c>
-      <c r="D40" t="n">
-        <v>6</v>
-      </c>
-      <c r="E40" t="n">
-        <v>6</v>
-      </c>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="n">
-        <v>3</v>
-      </c>
-      <c r="H40" t="n">
-        <v>3</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" t="n">
-        <v>7</v>
-      </c>
-      <c r="L40" t="inlineStr">
         <is>
           <t>C9</t>
         </is>
